--- a/myposapp/myapp/fixtures/DATA.xlsx
+++ b/myposapp/myapp/fixtures/DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pythonProject\MYPROJECT\myposapp\myapp\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62301EB-AFD2-457B-8AE6-7A766FE07F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E96A330-1B16-41BB-8C42-04E07BA89D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1410" yWindow="3135" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{5B43EEB1-D3BF-438C-ADAC-DFD6A9A41E7E}"/>
+    <workbookView xWindow="1140" yWindow="1725" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{5B43EEB1-D3BF-438C-ADAC-DFD6A9A41E7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Member" sheetId="1" r:id="rId1"/>
@@ -35,125 +35,68 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="66">
   <si>
     <t>ESPRESSO</t>
   </si>
   <si>
-    <t>“ESPRESSO.jpg“</t>
-  </si>
-  <si>
     <t>ช็อตกาแฟเข้มข้น</t>
   </si>
   <si>
-    <t>GOT</t>
-  </si>
-  <si>
     <t>AMERICANO</t>
   </si>
   <si>
-    <t>“AMERICANO.jpg“</t>
-  </si>
-  <si>
     <t>กาแฟดำ</t>
   </si>
   <si>
-    <t>JOHN</t>
-  </si>
-  <si>
     <t>CAPPUCCINO</t>
   </si>
   <si>
-    <t>“CAPPUCCINO.jpg“</t>
-  </si>
-  <si>
     <t>คาปูชิโน่</t>
   </si>
   <si>
-    <t>JINNY</t>
-  </si>
-  <si>
     <t>LATTE MACCHIATO</t>
   </si>
   <si>
-    <t>“LATTE MACCHIATO.jpg“</t>
-  </si>
-  <si>
     <t>ลัตเตมักกีอาโต</t>
   </si>
   <si>
-    <t>PLOY</t>
-  </si>
-  <si>
     <t>MATCHA </t>
   </si>
   <si>
     <t>ชาเขียว</t>
   </si>
   <si>
-    <t>SAMSON</t>
-  </si>
-  <si>
     <t>MATCHA LATTE</t>
   </si>
   <si>
-    <t>“MATCHA LATTE.jpg“</t>
-  </si>
-  <si>
     <t>มัทฉะลาเต้</t>
   </si>
   <si>
-    <t>TATAR</t>
-  </si>
-  <si>
     <t>BLACK TEA</t>
   </si>
   <si>
-    <t>“BLACK TEA.jpg“</t>
-  </si>
-  <si>
     <t>ชาดำ</t>
   </si>
   <si>
-    <t>YOK</t>
-  </si>
-  <si>
     <t>CORTADO </t>
   </si>
   <si>
-    <t>“CORTADO.jpg“ </t>
-  </si>
-  <si>
     <t>กอร์ตาโด</t>
   </si>
   <si>
-    <t>BOY</t>
-  </si>
-  <si>
     <t>MOKACCINO</t>
   </si>
   <si>
-    <t>“MOKACCINO.jpg“</t>
-  </si>
-  <si>
     <t>มอคคาชิโนมอคค่า</t>
   </si>
   <si>
-    <t>Joy</t>
-  </si>
-  <si>
     <t>MAROCCHINO</t>
   </si>
   <si>
-    <t>“MAROCCHINO.jpg“</t>
-  </si>
-  <si>
     <t>มารอคคีโน่</t>
   </si>
   <si>
-    <t>Jib</t>
-  </si>
-  <si>
     <t>antipode</t>
   </si>
   <si>
@@ -214,18 +157,12 @@
     <t>08MVAE5T</t>
   </si>
   <si>
-    <t>“MATCHA .jpg“</t>
-  </si>
-  <si>
     <t>username</t>
   </si>
   <si>
     <t>password</t>
   </si>
   <si>
-    <t>product_Name</t>
-  </si>
-  <si>
     <t>img_product</t>
   </si>
   <si>
@@ -235,13 +172,67 @@
     <t>price</t>
   </si>
   <si>
-    <t>order_id</t>
-  </si>
-  <si>
-    <t>number</t>
-  </si>
-  <si>
-    <t>name_customer</t>
+    <t>Coffee</t>
+  </si>
+  <si>
+    <t>Cake</t>
+  </si>
+  <si>
+    <t>เค้ก</t>
+  </si>
+  <si>
+    <t>Desserts</t>
+  </si>
+  <si>
+    <t>Cereal</t>
+  </si>
+  <si>
+    <t>ซีเรียล</t>
+  </si>
+  <si>
+    <t>Breakfast</t>
+  </si>
+  <si>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>ESPRESSO.jpg</t>
+  </si>
+  <si>
+    <t>AMERICANO.jpg</t>
+  </si>
+  <si>
+    <t>CAPPUCCINO.jpg</t>
+  </si>
+  <si>
+    <t>LATTE MACCHIATO.jpg</t>
+  </si>
+  <si>
+    <t>MATCHA .jpg</t>
+  </si>
+  <si>
+    <t>MATCHA LATTE.jpg</t>
+  </si>
+  <si>
+    <t>BLACK TEA.jpg</t>
+  </si>
+  <si>
+    <t>CORTADO.jpg</t>
+  </si>
+  <si>
+    <t>MOKACCINO.jpg</t>
+  </si>
+  <si>
+    <t>MAROCCHINO.jpg</t>
+  </si>
+  <si>
+    <t>Cake.jpg</t>
+  </si>
+  <si>
+    <t>Cereal.jpg</t>
   </si>
 </sst>
 </file>
@@ -283,7 +274,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -319,11 +310,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -341,6 +343,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -666,90 +674,90 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -759,7 +767,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55D6DA0D-7FC9-4B5D-B4A8-3AE3CEFC9CED}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" customWidth="1"/>
@@ -771,257 +779,225 @@
     <col min="7" max="7" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2">
+        <v>50</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2">
-        <v>50</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2">
-        <v>914365485</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="B3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="D3" s="2">
+        <v>50</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D4" s="2">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2">
-        <v>50</v>
-      </c>
-      <c r="E3" s="2">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2">
-        <v>912365485</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="B5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="D5" s="2">
+        <v>50</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D6" s="3">
+        <v>50</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2">
-        <v>50</v>
-      </c>
-      <c r="E4" s="2">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2">
-        <v>912365489</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="B7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="D7" s="2">
+        <v>50</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D8" s="2">
+        <v>50</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2">
-        <v>50</v>
-      </c>
-      <c r="E5" s="2">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2">
-        <v>912365269</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="B9" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="D9" s="2">
+        <v>50</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="3">
-        <v>50</v>
-      </c>
-      <c r="E6" s="3">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3">
-        <v>951915569</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="D10" s="2">
+        <v>50</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="B11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="2">
-        <v>50</v>
-      </c>
-      <c r="E7" s="2">
-        <v>6</v>
-      </c>
-      <c r="F7" s="2">
-        <v>914654190</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2">
-        <v>50</v>
-      </c>
-      <c r="E8" s="2">
-        <v>7</v>
-      </c>
-      <c r="F8" s="2">
-        <v>932554385</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="2">
-        <v>50</v>
-      </c>
-      <c r="E9" s="2">
-        <v>8</v>
-      </c>
-      <c r="F9" s="2">
-        <v>914189489</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="2">
-        <v>50</v>
-      </c>
-      <c r="E10" s="2">
-        <v>9</v>
-      </c>
-      <c r="F10" s="2">
-        <v>945189469</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="D11" s="2">
         <v>50</v>
       </c>
-      <c r="E11" s="2">
-        <v>10</v>
-      </c>
-      <c r="F11" s="2">
-        <v>945185969</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>38</v>
+      <c r="E11" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="8">
+        <v>50</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="8">
+        <v>50</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/myposapp/myapp/fixtures/DATA.xlsx
+++ b/myposapp/myapp/fixtures/DATA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pythonProject\MYPROJECT\myposapp\myapp\fixtures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAFE-POS-Project\myposapp\myapp\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E96A330-1B16-41BB-8C42-04E07BA89D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34A8113-DC01-40F9-93A2-6C52813291CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1725" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{5B43EEB1-D3BF-438C-ADAC-DFD6A9A41E7E}"/>
+    <workbookView xWindow="6060" yWindow="5640" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{5B43EEB1-D3BF-438C-ADAC-DFD6A9A41E7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Member" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="81">
   <si>
     <t>ESPRESSO</t>
   </si>
@@ -233,13 +233,58 @@
   </si>
   <si>
     <t>Cereal.jpg</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>antipode@gmil.com</t>
+  </si>
+  <si>
+    <t>rachilla@gmil.com</t>
+  </si>
+  <si>
+    <t>blockers@gmil.com</t>
+  </si>
+  <si>
+    <t>clamored@gmil.com</t>
+  </si>
+  <si>
+    <t>accompli@gmil.com</t>
+  </si>
+  <si>
+    <t>cubicles@gmil.com</t>
+  </si>
+  <si>
+    <t>croupade@gmil.com</t>
+  </si>
+  <si>
+    <t>sunbeamy@gmil.com</t>
+  </si>
+  <si>
+    <t>backrest@gmil.com</t>
+  </si>
+  <si>
+    <t>slushing@gmil.com</t>
+  </si>
+  <si>
+    <t>Fried Rice</t>
+  </si>
+  <si>
+    <t>Fried Rice.jpg</t>
+  </si>
+  <si>
+    <t>ข้าวผัด</t>
+  </si>
+  <si>
+    <t>lunch</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +309,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -322,10 +375,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -351,8 +405,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -665,109 +729,155 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CE50B92-27B4-42E3-9AD6-EB2010F21412}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.28515625" customWidth="1"/>
     <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{8E4CC070-0FA2-4C0E-9EA3-172283403B28}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{219CB4F2-1188-489E-8F13-C049D54C3DFE}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{6BBAE801-8D4A-42A5-A1B5-340B3433C20A}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{C52A67FA-7F25-40EE-BE6C-30E999B6390A}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{DC8D90FF-7D0E-404B-8338-F1E73851D3D5}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{14000E30-FF01-45FB-9D1B-442AADE040CB}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{DE14A506-E0FE-4411-8020-CDE44E9885FF}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{E31C88DF-D680-407D-98DF-4717E1A65F69}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{9E0E04D5-0A6D-497A-8A47-2E0EDED646A1}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{A6CBA262-7AD2-42B9-8656-650919D11309}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55D6DA0D-7FC9-4B5D-B4A8-3AE3CEFC9CED}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" customWidth="1"/>
@@ -1000,6 +1110,23 @@
         <v>51</v>
       </c>
     </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="11">
+        <v>60</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/myposapp/myapp/fixtures/DATA.xlsx
+++ b/myposapp/myapp/fixtures/DATA.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAFE-POS-Project\myposapp\myapp\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D25556-8867-459D-85C3-ABF8C95C3685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165B2E38-B96A-4C17-9B30-B4F8735B85C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5B43EEB1-D3BF-438C-ADAC-DFD6A9A41E7E}"/>
+    <workbookView xWindow="6645" yWindow="3465" windowWidth="21600" windowHeight="9390" xr2:uid="{5B43EEB1-D3BF-438C-ADAC-DFD6A9A41E7E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Category" sheetId="3" r:id="rId1"/>
-    <sheet name="Product" sheetId="4" r:id="rId2"/>
-    <sheet name="Option" sheetId="5" r:id="rId3"/>
+    <sheet name="Store" sheetId="11" r:id="rId1"/>
+    <sheet name="Category" sheetId="3" r:id="rId2"/>
+    <sheet name="Ingredient" sheetId="9" r:id="rId3"/>
+    <sheet name="Product" sheetId="4" r:id="rId4"/>
+    <sheet name="ProductIngredient" sheetId="10" r:id="rId5"/>
+    <sheet name="Option" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="77">
   <si>
     <t>img_product</t>
   </si>
@@ -206,17 +209,91 @@
     <t>Sirup</t>
   </si>
   <si>
-    <t>Sugar</t>
+    <t>CafePOS2</t>
+  </si>
+  <si>
+    <t>store</t>
+  </si>
+  <si>
+    <t>Snacks</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>reorder Level</t>
+  </si>
+  <si>
+    <t>นม</t>
+  </si>
+  <si>
+    <t>เมล็ดกาแฟ</t>
+  </si>
+  <si>
+    <t>น้ำตาล</t>
+  </si>
+  <si>
+    <t>มิลลิลิตร</t>
+  </si>
+  <si>
+    <t>ชิ้น</t>
+  </si>
+  <si>
+    <t>โซดา</t>
+  </si>
+  <si>
+    <t>กรัม</t>
+  </si>
+  <si>
+    <t>เลม่อน</t>
+  </si>
+  <si>
+    <t>ลูก</t>
+  </si>
+  <si>
+    <t>ingredient</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>Latte</t>
+  </si>
+  <si>
+    <t>LATTE.jpg</t>
+  </si>
+  <si>
+    <t>ลาเต้</t>
+  </si>
+  <si>
+    <t>owner</t>
+  </si>
+  <si>
+    <t>admin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -230,7 +307,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -238,14 +315,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -560,41 +655,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1842C4EC-8C1B-4FB6-B7C8-A86DDE42C100}">
-  <dimension ref="A1:A6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{261D1C3A-0235-46B7-9933-9E2C93E56E49}">
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="3" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
+      <c r="B1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -603,8 +685,289 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1842C4EC-8C1B-4FB6-B7C8-A86DDE42C100}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="59.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2124681-FCDA-4100-8840-F33A54D8D883}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="5" max="5" width="44.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D2" s="1">
+        <v>300</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D3" s="1">
+        <v>300</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D4" s="1">
+        <v>300</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="1">
+        <v>500</v>
+      </c>
+      <c r="D6" s="1">
+        <v>200</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D7" s="1">
+        <v>300</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D8" s="1">
+        <v>300</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="1">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="1">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1">
+        <v>5</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="1">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98EEAC6E-2A1F-4C7E-96B4-B0482816E370}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
@@ -632,7 +995,7 @@
         <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -651,8 +1014,8 @@
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1">
-        <v>10</v>
+      <c r="F2" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -671,8 +1034,8 @@
       <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1">
-        <v>3</v>
+      <c r="F3" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -691,8 +1054,8 @@
       <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="1">
-        <v>6</v>
+      <c r="F4" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -711,8 +1074,8 @@
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1">
-        <v>2</v>
+      <c r="F5" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -731,8 +1094,8 @@
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="1">
-        <v>7</v>
+      <c r="F6" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -751,8 +1114,8 @@
       <c r="E7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="1">
-        <v>10</v>
+      <c r="F7" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -771,8 +1134,8 @@
       <c r="E8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="1">
-        <v>7</v>
+      <c r="F8" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -791,8 +1154,8 @@
       <c r="E9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="1">
-        <v>6</v>
+      <c r="F9" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -811,8 +1174,8 @@
       <c r="E10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="1">
-        <v>8</v>
+      <c r="F10" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -831,23 +1194,277 @@
       <c r="E11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="1">
+        <v>50</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EEB1B7-24E4-4603-93B5-4CCEE963C6F7}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="41.28515625" customWidth="1"/>
+    <col min="3" max="3" width="53.140625" customWidth="1"/>
+    <col min="4" max="4" width="46.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="1">
+        <v>200</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="1">
+        <v>50</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="1">
+        <v>50</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="1">
+        <v>50</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="1">
+        <v>30</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="1">
+        <v>30</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="1">
+        <v>30</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1">
+        <v>50</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1">
+        <v>200</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{820D21BC-226E-4339-A4A2-22A665E86D15}">
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" customWidth="1"/>
     <col min="16" max="16" width="17.42578125" customWidth="1"/>
     <col min="17" max="17" width="14.28515625" customWidth="1"/>
   </cols>
@@ -1084,26 +1701,14 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="1">
-        <v>5</v>
-      </c>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="1">
-        <v>5</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
